--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1092,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1133,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2610,22 +2642,22 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2658,12 +2690,12 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2677,7 +2709,7 @@
       <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2713,7 +2745,1121 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -981,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq61，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1966,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2029,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2218,12 +2274,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2251,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2259,10 +2315,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2362,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3433,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3544,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3583,7 +3655,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3694,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3805,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3854,12 +3926,813 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
           <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1473,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1506,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,33 +1534,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1703,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1736,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,33 +1772,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1847,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,17 +1891,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1891,13 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1954,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2279,7 +2303,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2307,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2767,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2878,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3679,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3790,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3931,7 +3955,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4016,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4161,7 +4185,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4246,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4337,7 +4361,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4448,7 +4472,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4502,7 +4526,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4587,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4625,22 +4649,22 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4673,12 +4697,12 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4727,12 +4751,242 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>142.0</t>
         </is>
       </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1840,24 +1840,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq52，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2076,32 +2076,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,33 +2137,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2187,32 +2195,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2220,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,33 +2256,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2319,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq57，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2331,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2513,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2536,32 +2552,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2569,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,33 +2613,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2647,32 +2671,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2680,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,33 +2732,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2973,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2980,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3013,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3037,33 +3073,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3091,32 +3131,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3124,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3148,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3168,13 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3202,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3235,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3259,17 +3311,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3279,13 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3955,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4185,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4528,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4526,7 +4582,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4641,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4756,7 +4812,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4871,7 +4927,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4986,7 +5042,1030 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
           <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3141,24 +3141,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3260,24 +3260,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3480,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3541,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3557,13 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3591,32 +3599,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3624,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,17 +3660,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3668,13 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3702,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3735,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,17 +3779,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3779,13 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3837,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3846,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,33 +3898,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3924,32 +3956,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3957,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,17 +4017,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4001,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4039,32 +4075,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4072,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4096,17 +4136,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4116,7 +4156,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4126,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4194,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4187,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,37 +4255,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4313,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4302,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,32 +4374,32 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4384,12 +4432,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4417,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,10 +4473,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4495,32 +4559,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4528,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4552,17 +4620,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4572,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4697,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4797,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4812,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5042,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5157,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5272,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5387,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5502,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5839,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5954,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6069,6 +6137,692 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,13 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,17 +2637,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,7 +2751,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2762,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2877,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2988,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3456,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4441,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4535,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4678,32 +4682,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4711,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4743,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4755,17 +4763,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4793,32 +4801,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4826,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4862,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,17 +4882,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4908,32 +4920,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4941,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,37 +4981,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5039,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5056,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5100,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5158,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5171,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5219,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,17 +5239,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5392,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5401,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,37 +5453,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5511,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5516,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,17 +5572,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5560,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5630,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5631,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5691,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,13 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5792,7 +5832,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5907,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6022,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6133,7 +6173,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6244,7 +6284,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6359,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6474,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6589,7 +6629,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6704,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6809,17 +6849,584 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>18/28</t>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,13 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,22 +3215,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,14 +3334,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,13 +3454,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,14 +3568,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3575,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,12 +3930,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4051,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,14 +4647,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -4654,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4892,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,14 +5595,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -5602,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5640,24 +5648,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5667,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5716,7 +5724,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5860,32 +5868,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5893,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5929,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5937,17 +5949,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5987,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6008,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,37 +6048,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6106,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6123,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6167,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,13 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6201,32 +6225,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6234,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6286,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6278,13 +6306,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6312,32 +6344,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6345,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,37 +6405,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6427,32 +6463,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6460,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,17 +6524,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6504,12 +6544,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6575,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6629,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6744,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6859,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7146,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7200,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7416,17 +7456,822 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>13/29</t>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,22 +1549,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4282,22 +4282,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4885,22 +4885,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,14 +5242,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6247,12 +6247,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6354,24 +6354,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6473,24 +6473,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6582,32 +6582,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,37 +6643,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6697,32 +6701,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6730,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6762,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6774,17 +6782,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6812,32 +6820,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6845,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,37 +6881,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6927,32 +6939,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6960,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6984,17 +7000,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7004,17 +7020,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7058,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7075,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,10 +7099,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:35</t>
@@ -7186,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7301,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7372,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7412,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7581,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7681,7 +7713,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7696,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7872,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7926,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7987,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8041,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8151,12 +8183,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,6 +8307,692 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,22 +4647,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5481,17 +5481,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6949,24 +6949,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7185,32 +7185,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7218,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7246,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7262,17 +7266,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7387,7 @@
       <c r="AB58" s="2" t="inlineStr"/>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7411,32 +7415,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7444,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7488,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7514,7 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -7554,12 +7562,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7608,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7621,22 +7629,22 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7669,12 +7677,12 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7696,7 @@
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7713,22 +7721,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7736,52 +7744,56 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7789,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7815,7 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7813,37 +7825,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7863,7 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7871,40 +7883,44 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,37 +7944,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7966,22 +7982,22 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8014,12 +8030,12 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8033,7 +8049,7 @@
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -8068,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8081,22 +8097,22 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8129,12 +8145,12 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8148,7 +8164,7 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -8173,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8196,22 +8212,22 @@
       <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8249,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8263,7 +8279,7 @@
       <c r="T66" s="2" t="inlineStr"/>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
@@ -8288,22 +8304,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8311,22 +8327,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8364,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8394,7 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
@@ -8403,22 +8419,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8426,22 +8442,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8474,12 +8490,12 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8493,7 +8509,7 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
@@ -8518,22 +8534,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8541,22 +8557,22 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8589,12 +8605,12 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8608,7 +8624,7 @@
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8638,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8656,22 +8672,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8704,12 +8720,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8723,7 +8739,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8748,22 +8764,18 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8783,7 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -8781,7 +8793,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8819,12 +8831,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8989,7 +9001,348 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,14 +4163,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6425,17 +6425,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7649,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7682,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7726,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7774,24 +7778,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7801,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7854,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7893,24 +7897,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8002,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8035,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8079,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8117,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8150,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,37 +8186,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8265,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8309,12 +8325,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8347,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8380,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8424,12 +8444,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8495,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8610,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8664,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8836,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8947,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9001,7 +9021,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9116,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,22 +9259,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9287,12 +9307,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9306,43 +9326,1074 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,22 +2632,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5595,22 +5595,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,22 +7606,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8016,24 +8016,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8125,36 +8125,32 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8162,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,17 +8182,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8206,12 +8202,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8244,36 +8240,32 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8281,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8325,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8400,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8439,14 +8431,14 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -8454,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8597,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8630,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,37 +8650,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8823,12 +8819,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8856,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,10 +8860,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8934,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8967,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,17 +9007,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9011,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9136,7 +9152,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9312,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9366,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9538,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9879,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10109,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10224,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10268,12 +10284,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10286,22 +10302,22 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10334,12 +10350,12 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10353,47 +10369,852 @@
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>131.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="W85" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y84" s="2" t="inlineStr">
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC84" s="2" t="inlineStr">
+      <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>149.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,22 +3687,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,17 +5242,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8599,24 +8599,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8956,24 +8956,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9022,17 +9022,17 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9065,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,37 +9126,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9554,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9665,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9780,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9819,7 +9823,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9895,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10010,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10240,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10585,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10700,7 +10704,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10815,7 +10819,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10930,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11045,7 +11049,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11099,7 +11103,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11164,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11209,12 +11213,698 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2871,13 +2871,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>191.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,14 +3100,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3529,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3573,17 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,7 +3701,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3821,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3929,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4005,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4167,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4366,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4608,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4727,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4766,22 +4770,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,22 +5127,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5261,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5357,7 +5361,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5556,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5610,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5714,7 +5718,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5790,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5834,13 +5838,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>191.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6024,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,14 +6071,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -6078,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6262,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,7 +6309,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6381,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,7 +6547,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6673,7 +6681,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6911,7 +6919,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7222,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7337,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7452,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,14 +7971,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -7978,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,17 +8210,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8446,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8680,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8832,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8852,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9045,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9075,24 +9083,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9102,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9151,7 +9159,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9217,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9256,7 +9264,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9299,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9332,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,37 +9368,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>147.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9525,32 +9537,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>191分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9558,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9582,17 +9598,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9602,13 +9618,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>191.0</t>
+        </is>
+      </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9636,32 +9656,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9669,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,37 +9717,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9823,7 +9847,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9866,32 +9890,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9899,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9923,37 +9951,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10053,7 +10081,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10129,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,32 +10239,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10244,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10268,17 +10300,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10288,17 +10320,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10474,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10513,7 +10545,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10589,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10643,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10819,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10934,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11049,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11103,7 +11135,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11218,7 +11250,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11258,7 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -11236,7 +11268,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11274,12 +11306,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11293,7 +11325,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -11318,18 +11350,22 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB92" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11337,22 +11373,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11390,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11404,7 +11440,7 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -11429,22 +11465,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11452,22 +11488,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11500,12 +11536,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11519,7 +11555,7 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11549,17 +11585,13 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>128.7</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11669,7 +11701,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11735,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11789,7 +11821,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11889,22 +11921,942 @@
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA97" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>147.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="AC97" s="2" t="inlineStr">
+      <c r="AC100" s="2" t="inlineStr">
         <is>
           <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5957,17 +5957,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7274,17 +7274,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10249,24 +10249,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10358,32 +10358,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10391,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,17 +10419,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10435,17 +10439,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10621,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10703,32 +10707,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10736,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10768,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10780,17 +10788,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10890,7 +10898,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10933,32 +10941,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10966,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10990,17 +11002,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11010,17 +11022,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11048,32 +11060,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11081,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11105,17 +11121,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11125,12 +11141,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11163,32 +11179,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11196,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11220,17 +11240,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11240,12 +11260,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11311,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11426,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11541,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11652,7 +11672,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11787,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11882,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11936,7 +11956,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11997,7 +12017,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12112,7 +12132,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12166,7 +12186,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12174,22 +12194,22 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:35</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12222,12 +12242,12 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12241,7 +12261,7 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
@@ -12266,22 +12286,22 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12289,22 +12309,22 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12337,12 +12357,12 @@
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12386,17 +12406,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12424,7 @@
       <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -12414,7 +12434,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -12457,7 +12477,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12471,7 +12491,7 @@
       <c r="T102" s="2" t="inlineStr"/>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
@@ -12496,7 +12516,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12506,12 +12526,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12549,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -12572,7 +12592,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12586,7 +12606,7 @@
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
@@ -12626,7 +12646,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12634,22 +12654,22 @@
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -12682,12 +12702,12 @@
       <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12701,7 +12721,7 @@
       <c r="T104" s="2" t="inlineStr"/>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
@@ -12731,17 +12751,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12769,7 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -12759,7 +12779,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -12797,12 +12817,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12816,47 +12836,277 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC105" s="2" t="inlineStr">
+      <c r="AC106" s="2" t="inlineStr">
         <is>
           <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6076,17 +6076,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7976,17 +7976,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9035,17 +9035,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9154,17 +9154,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11298,32 +11298,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11331,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11355,17 +11359,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11375,17 +11379,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11639,32 +11643,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11672,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11696,17 +11704,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11716,17 +11724,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11754,32 +11762,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11787,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11811,17 +11823,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11831,17 +11843,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11984,32 +11996,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12017,7 +12033,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12041,17 +12057,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12061,17 +12077,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>147.7</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12099,32 +12115,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12132,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12156,17 +12176,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12176,17 +12196,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12301,7 +12321,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12329,32 +12349,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12362,7 +12386,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12386,17 +12410,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12406,17 +12430,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12444,12 +12468,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12477,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12485,10 +12509,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>19:45</t>
@@ -12559,12 +12599,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq41，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12592,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12600,10 +12640,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
       <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
           <t>19:50</t>
@@ -12707,7 +12759,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12822,7 +12874,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12876,7 +12928,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12989,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13052,7 +13104,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">

--- a/data/export/2026-09-30-浦东35路.xlsx
+++ b/data/export/2026-09-30-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9737,17 +9737,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12234,32 +12234,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12267,7 +12271,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12291,17 +12295,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12311,17 +12315,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12477,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq41，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12501,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12604,7 +12608,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq41，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq30推进至seq58，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -12632,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12726,32 +12730,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12759,7 +12767,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12783,17 +12791,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12803,12 +12811,12 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12928,7 +12936,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12997,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13104,7 +13112,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
